--- a/results/Int Task Remove ACC -0.4/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC -0.4/Rando_10_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6482087198630053</v>
+        <v>0.6771250405522498</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6478894350609619</v>
+        <v>0.6751935214957723</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6478894350609619</v>
+        <v>0.675487961628332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6515167568055915</v>
+        <v>0.6786988784992998</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6540845868598391</v>
+        <v>0.6786988784992998</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6534392414368021</v>
+        <v>0.679280982945469</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6553549502490627</v>
+        <v>0.6741204781674901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6556923039016398</v>
+        <v>0.6741227367738067</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6579001942401432</v>
+        <v>0.6413786943612867</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6575809094380998</v>
+        <v>0.6388131229133558</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6559799682152493</v>
+        <v>0.6633994899656281</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6556652006258393</v>
+        <v>0.6734012147195427</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.654100397104056</v>
+        <v>0.6724433603134125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6464194930044802</v>
+        <v>0.671141376435755</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6467320019875735</v>
+        <v>0.6721082652671521</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6460934323834867</v>
+        <v>0.6721082652671521</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6560341747668503</v>
+        <v>0.6775090036260898</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6541184659545898</v>
+        <v>0.6881425221651412</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6490844431303462</v>
+        <v>0.6631457047467691</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6455903791584021</v>
+        <v>0.6578564594087379</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6396075363532954</v>
+        <v>0.6629356543593155</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6379840090672777</v>
+        <v>0.651958006348737</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6492493213914657</v>
+        <v>0.670050264256939</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6416587615445581</v>
+        <v>0.6748192088307401</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6734946388899155</v>
+        <v>0.6699757302484878</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6602571525955493</v>
+        <v>0.6782432560068662</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6590409957579266</v>
+        <v>0.6774940146932606</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6587194523495665</v>
+        <v>0.6265568983996748</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.656190018602703</v>
+        <v>0.6268761832017182</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6339070193377767</v>
+        <v>0.6204859699482164</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6339070193377767</v>
+        <v>0.624335456423271</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6185045562249243</v>
+        <v>0.6253000866483513</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5946380686041401</v>
+        <v>0.6343154164254065</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6012414121628004</v>
+        <v>0.6524008985146583</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5856461462016402</v>
+        <v>0.6527224419230184</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5820030142127935</v>
+        <v>0.6331399145014845</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5678655759651435</v>
+        <v>0.6422168426326316</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.56785428293356</v>
+        <v>0.6746181928685533</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5782800096914744</v>
+        <v>0.6713282247765007</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5345989741820766</v>
+        <v>0.656059019436334</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5413039550249884</v>
+        <v>0.6084147458246583</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5238855831105526</v>
+        <v>0.6061549075408705</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4803152193106733</v>
+        <v>0.6080186684078468</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4460026774751245</v>
+        <v>0.6077084180310701</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.461472898777478</v>
+        <v>0.6076948663931701</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4676974124584724</v>
+        <v>0.5842221975828805</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4738202888552151</v>
+        <v>0.6064990370123977</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4906195973110266</v>
+        <v>0.5866251493760086</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4935451084747016</v>
+        <v>0.6016225006467828</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4852572552594728</v>
+        <v>0.598571944824301</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4888055257830177</v>
+        <v>0.5966313913425567</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4924463991655476</v>
+        <v>0.5590483875604177</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4955918164533311</v>
+        <v>0.5590483875604177</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4979081198950364</v>
+        <v>0.5586017994932508</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.496905093362572</v>
+        <v>0.5375402955899685</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5011258125849544</v>
+        <v>0.5375402955899685</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5027425640520219</v>
+        <v>0.5673867514260019</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5033766164434753</v>
+        <v>0.566487620784106</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4950322980703289</v>
+        <v>0.5513855523113755</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4950322980703289</v>
+        <v>0.5733845831639379</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4922061655845889</v>
+        <v>0.5691638639415555</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4831713296620714</v>
+        <v>0.602733940282449</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4812330347866439</v>
+        <v>0.6167432539535878</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4845117098471129</v>
+        <v>0.5968609478754727</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4825847080032689</v>
+        <v>0.5956063947304662</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4851389864196162</v>
+        <v>0.59280510691421</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4685934631826638</v>
+        <v>0.5781812469970803</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4705204650265079</v>
+        <v>0.5781812469970803</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4709007321991023</v>
+        <v>0.5499117090258014</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4709007321991023</v>
+        <v>0.5392209040174447</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4744625543605475</v>
+        <v>0.5368134350116832</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4637386915688279</v>
+        <v>0.5283395547670966</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4595654030790964</v>
+        <v>0.5392178240997401</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4879289812042889</v>
+        <v>0.5379316504662995</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4869711267981586</v>
+        <v>0.5420349221602132</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4869711267981586</v>
+        <v>0.5565006796351735</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4866586178150653</v>
+        <v>0.5479929202958363</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4831464849925877</v>
+        <v>0.5012681047829068</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4831464849925877</v>
+        <v>0.5012681047829068</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4904267944627186</v>
+        <v>0.499354654576963</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4904426047069356</v>
+        <v>0.4996739393790065</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4986401136694961</v>
+        <v>0.4993433615453795</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4925578921864541</v>
+        <v>0.5008629929408286</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4944916698492483</v>
+        <v>0.497665627707761</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4983290419813316</v>
+        <v>0.4979555506276873</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4973486015120342</v>
+        <v>0.4979555506276873</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4967145491205808</v>
+        <v>0.4979555506276873</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4983471108318653</v>
+        <v>0.4986167062949411</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4983471108318653</v>
+        <v>0.4953899791797564</v>
       </c>
     </row>
   </sheetData>
